--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_18_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_18_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAD8DCA-E941-4470-A793-6B74B34CB757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FF6399-FF87-46DB-B665-43B2ED727FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,34 +55,82 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT POLYCAB 28 Aug 2025 6600 PE</t>
-  </si>
-  <si>
-    <t>12-08-2025</t>
-  </si>
-  <si>
-    <t>OPT JINDALSTEL 28 Aug 2025 1000 CE</t>
-  </si>
-  <si>
-    <t>13-08-2025</t>
-  </si>
-  <si>
-    <t>OPT BDL 28 Aug 2025 1500 CE</t>
-  </si>
-  <si>
-    <t>OPT IRCTC 28 Aug 2025 730 CE</t>
-  </si>
-  <si>
-    <t>14-08-2025</t>
-  </si>
-  <si>
-    <t>OPT KAYNES 28 Aug 2025 6100 CE</t>
-  </si>
-  <si>
-    <t>18-08-2025</t>
-  </si>
-  <si>
-    <t>OPT COFORGE 28 Aug 2025 1600 CE</t>
+    <t>OPT RVNL 30 Sep 2025 350 CE</t>
+  </si>
+  <si>
+    <t>17-09-2025</t>
+  </si>
+  <si>
+    <t>OPT BAJFINANCE 30 Sep 2025 1020 CE</t>
+  </si>
+  <si>
+    <t>15-09-2025</t>
+  </si>
+  <si>
+    <t>OPT TITAGARH 30 Sep 2025 960 CE</t>
+  </si>
+  <si>
+    <t>OPT HUDCO 30 Sep 2025 220 CE</t>
+  </si>
+  <si>
+    <t>OPT MOTHERSON 30 Sep 2025 105 CE</t>
+  </si>
+  <si>
+    <t>16-09-2025</t>
+  </si>
+  <si>
+    <t>OPT NTPC 30 Sep 2025 330 CE</t>
+  </si>
+  <si>
+    <t>OPT EICHERMOT 30 Sep 2025 6800 CE</t>
+  </si>
+  <si>
+    <t>OPT CHOLAFIN 30 Sep 2025 1560 CE</t>
+  </si>
+  <si>
+    <t>OPT CANBK 30 Sep 2025 115 CE</t>
+  </si>
+  <si>
+    <t>OPT MPHASIS 30 Sep 2025 3000 CE</t>
+  </si>
+  <si>
+    <t>OPT BEL 30 Sep 2025 400 CE</t>
+  </si>
+  <si>
+    <t>OPT PERSISTENT 30 Sep 2025 5600 CE</t>
+  </si>
+  <si>
+    <t>OPT COFORGE 30 Sep 2025 1800 CE</t>
+  </si>
+  <si>
+    <t>OPT DALBHARAT 30 Sep 2025 2480 CE</t>
+  </si>
+  <si>
+    <t>OPT IREDA 30 Sep 2025 150 CE</t>
+  </si>
+  <si>
+    <t>18-09-2025</t>
+  </si>
+  <si>
+    <t>OPT BANKBARODA 30 Sep 2025 250 CE</t>
+  </si>
+  <si>
+    <t>OPT ASIANPAINT 30 Sep 2025 2480 CE</t>
+  </si>
+  <si>
+    <t>19-09-2025</t>
+  </si>
+  <si>
+    <t>OPT KAYNES 30 Sep 2025 7300 CE</t>
+  </si>
+  <si>
+    <t>OPT LAURUSLABS 30 Sep 2025 930 CE</t>
+  </si>
+  <si>
+    <t>OPT IRCTC 30 Sep 2025 730 CE</t>
+  </si>
+  <si>
+    <t>OPT INOXWIND 30 Sep 2025 150 CE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -435,10 +483,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38.28515625" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -454,10 +502,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -466,10 +514,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -492,284 +540,1036 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45881</v>
+        <v>45915</v>
       </c>
       <c r="D2">
-        <v>125</v>
+        <v>1375</v>
       </c>
       <c r="E2">
-        <v>135.25</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>16906.25</v>
+        <v>15125</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>125</v>
+        <v>1375</v>
       </c>
       <c r="I2">
-        <v>118</v>
+        <v>12.8</v>
       </c>
       <c r="J2">
-        <v>14750</v>
+        <v>17600</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>-2156.25</v>
+        <v>2475</v>
       </c>
       <c r="M2">
-        <v>76.510000000000005</v>
+        <v>79.010000000000005</v>
       </c>
       <c r="N2">
-        <v>-2232.7600000000002</v>
+        <v>2395.9899999999998</v>
       </c>
       <c r="O2">
-        <v>2156.25</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>139</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45882</v>
+        <v>45915</v>
       </c>
       <c r="D3">
-        <v>625</v>
+        <v>1500</v>
       </c>
       <c r="E3">
-        <v>30.5</v>
+        <v>19.28</v>
       </c>
       <c r="F3">
-        <v>19062.5</v>
+        <v>28912.5</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H3">
-        <v>625</v>
+        <v>1500</v>
       </c>
       <c r="I3">
-        <v>27.5</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="J3">
-        <v>17187.5</v>
+        <v>26850</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>-1875</v>
+        <v>-2062.5</v>
       </c>
       <c r="M3">
-        <v>80.2</v>
+        <v>121.96</v>
       </c>
       <c r="N3">
-        <v>-1955.2</v>
+        <v>-2184.46</v>
       </c>
       <c r="O3">
-        <v>1875</v>
+        <v>2062.5</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>40</v>
+        <v>280</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="1">
-        <v>45882</v>
+        <v>45915</v>
       </c>
       <c r="D4">
-        <v>325</v>
+        <v>725</v>
       </c>
       <c r="E4">
-        <v>70</v>
+        <v>33.5</v>
       </c>
       <c r="F4">
-        <v>22750</v>
+        <v>24287.5</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H4">
-        <v>325</v>
+        <v>725</v>
       </c>
       <c r="I4">
-        <v>81</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="J4">
-        <v>26325</v>
+        <v>25157.5</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>3575</v>
+        <v>870</v>
       </c>
       <c r="M4">
-        <v>95.08</v>
+        <v>93.88</v>
       </c>
       <c r="N4">
-        <v>3479.92</v>
+        <v>776.12</v>
       </c>
       <c r="O4">
-        <v>3575</v>
+        <v>870</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>45883</v>
+        <v>45915</v>
       </c>
       <c r="D5">
-        <v>875</v>
+        <v>2775</v>
       </c>
       <c r="E5">
-        <v>11.95</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F5">
-        <v>10456.25</v>
+        <v>22755</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H5">
-        <v>875</v>
+        <v>2775</v>
       </c>
       <c r="I5">
-        <v>11.55</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="J5">
-        <v>10106.25</v>
+        <v>25530</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>-350</v>
+        <v>2775</v>
       </c>
       <c r="M5">
-        <v>66.27</v>
+        <v>94.44</v>
       </c>
       <c r="N5">
-        <v>-416.27</v>
+        <v>2680.56</v>
       </c>
       <c r="O5">
-        <v>350</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45916</v>
+      </c>
+      <c r="D6">
+        <v>6150</v>
+      </c>
+      <c r="E6">
+        <v>5.05</v>
+      </c>
+      <c r="F6">
+        <v>31057.5</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1">
-        <v>45883</v>
-      </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
-      <c r="E6">
-        <v>210</v>
-      </c>
-      <c r="F6">
-        <v>21000</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="H6">
-        <v>100</v>
+        <v>6150</v>
       </c>
       <c r="I6">
-        <v>260</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="J6">
-        <v>26000</v>
+        <v>30135</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>5000</v>
+        <v>-922.5</v>
       </c>
       <c r="M6">
-        <v>93.6</v>
+        <v>104.38</v>
       </c>
       <c r="N6">
-        <v>4906.3999999999996</v>
+        <v>-1026.8800000000001</v>
       </c>
       <c r="O6">
-        <v>5000</v>
+        <v>922.5</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>61</v>
+        <v>219</v>
       </c>
       <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45916</v>
+      </c>
+      <c r="D7">
+        <v>1500</v>
+      </c>
+      <c r="E7">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="F7">
+        <v>12075</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>1500</v>
+      </c>
+      <c r="I7">
+        <v>8.1</v>
+      </c>
+      <c r="J7">
+        <v>12150</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>75</v>
+      </c>
+      <c r="M7">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="N7">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O7">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>101</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1">
-        <v>45883</v>
-      </c>
-      <c r="D7">
-        <v>375</v>
-      </c>
-      <c r="E7">
-        <v>62.3</v>
-      </c>
-      <c r="F7">
-        <v>23362.5</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>375</v>
-      </c>
-      <c r="I7">
+      <c r="C8" s="1">
+        <v>45916</v>
+      </c>
+      <c r="D8">
+        <v>175</v>
+      </c>
+      <c r="E8">
+        <v>149.85</v>
+      </c>
+      <c r="F8">
+        <v>26223.75</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8">
+        <v>175</v>
+      </c>
+      <c r="I8">
+        <v>161</v>
+      </c>
+      <c r="J8">
+        <v>28175</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>1951.25</v>
+      </c>
+      <c r="M8">
+        <v>99.04</v>
+      </c>
+      <c r="N8">
+        <v>1852.21</v>
+      </c>
+      <c r="O8">
+        <v>1951.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45916</v>
+      </c>
+      <c r="D9">
+        <v>625</v>
+      </c>
+      <c r="E9">
+        <v>36.85</v>
+      </c>
+      <c r="F9">
+        <v>23031.25</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9">
+        <v>625</v>
+      </c>
+      <c r="I9">
+        <v>39</v>
+      </c>
+      <c r="J9">
+        <v>24375</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>1343.75</v>
+      </c>
+      <c r="M9">
+        <v>92.2</v>
+      </c>
+      <c r="N9">
+        <v>1251.55</v>
+      </c>
+      <c r="O9">
+        <v>1343.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>56</v>
       </c>
-      <c r="J7">
-        <v>21000</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>-2362.5</v>
-      </c>
-      <c r="M7">
-        <v>87.81</v>
-      </c>
-      <c r="N7">
-        <v>-2450.31</v>
-      </c>
-      <c r="O7">
-        <v>2362.5</v>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45917</v>
+      </c>
+      <c r="D10">
+        <v>6750</v>
+      </c>
+      <c r="E10">
+        <v>2.95</v>
+      </c>
+      <c r="F10">
+        <v>19912.5</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10">
+        <v>6750</v>
+      </c>
+      <c r="I10">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="J10">
+        <v>16537.5</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>-3375</v>
+      </c>
+      <c r="M10">
+        <v>79.66</v>
+      </c>
+      <c r="N10">
+        <v>-3454.66</v>
+      </c>
+      <c r="O10">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>180</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45917</v>
+      </c>
+      <c r="D11">
+        <v>275</v>
+      </c>
+      <c r="E11">
+        <v>79.349999999999994</v>
+      </c>
+      <c r="F11">
+        <v>21821.25</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11">
+        <v>275</v>
+      </c>
+      <c r="I11">
+        <v>67.7</v>
+      </c>
+      <c r="J11">
+        <v>18617.5</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>-3203.75</v>
+      </c>
+      <c r="M11">
+        <v>83.47</v>
+      </c>
+      <c r="N11">
+        <v>-3287.22</v>
+      </c>
+      <c r="O11">
+        <v>3203.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45917</v>
+      </c>
+      <c r="D12">
+        <v>2850</v>
+      </c>
+      <c r="E12">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="F12">
+        <v>48022.5</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12">
+        <v>2850</v>
+      </c>
+      <c r="I12">
+        <v>15.3</v>
+      </c>
+      <c r="J12">
+        <v>43605</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>-4417.5</v>
+      </c>
+      <c r="M12">
+        <v>130.57</v>
+      </c>
+      <c r="N12">
+        <v>-4548.07</v>
+      </c>
+      <c r="O12">
+        <v>4417.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>227</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45917</v>
+      </c>
+      <c r="D13">
+        <v>100</v>
+      </c>
+      <c r="E13">
+        <v>177.4</v>
+      </c>
+      <c r="F13">
+        <v>17740</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
+        <v>183.25</v>
+      </c>
+      <c r="J13">
+        <v>18325</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>585</v>
+      </c>
+      <c r="M13">
+        <v>81.22</v>
+      </c>
+      <c r="N13">
+        <v>503.78</v>
+      </c>
+      <c r="O13">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>63</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45917</v>
+      </c>
+      <c r="D14">
+        <v>1125</v>
+      </c>
+      <c r="E14">
+        <v>46.35</v>
+      </c>
+      <c r="F14">
+        <v>52143.75</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14">
+        <v>1125</v>
+      </c>
+      <c r="I14">
+        <v>43.08</v>
+      </c>
+      <c r="J14">
+        <v>48468.75</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>-3675</v>
+      </c>
+      <c r="M14">
+        <v>210.33</v>
+      </c>
+      <c r="N14">
+        <v>-3885.33</v>
+      </c>
+      <c r="O14">
+        <v>3675</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>75</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="1">
+        <v>45917</v>
+      </c>
+      <c r="D15">
+        <v>325</v>
+      </c>
+      <c r="E15">
+        <v>50.25</v>
+      </c>
+      <c r="F15">
+        <v>16331.25</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15">
+        <v>325</v>
+      </c>
+      <c r="I15">
+        <v>48.5</v>
+      </c>
+      <c r="J15">
+        <v>15762.5</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>-568.75</v>
+      </c>
+      <c r="M15">
+        <v>76.94</v>
+      </c>
+      <c r="N15">
+        <v>-645.69000000000005</v>
+      </c>
+      <c r="O15">
+        <v>568.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>134</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1">
+        <v>45918</v>
+      </c>
+      <c r="D16">
+        <v>3450</v>
+      </c>
+      <c r="E16">
+        <v>9.25</v>
+      </c>
+      <c r="F16">
+        <v>31912.5</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16">
+        <v>3450</v>
+      </c>
+      <c r="I16">
+        <v>10.3</v>
+      </c>
+      <c r="J16">
+        <v>35535</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>3622.5</v>
+      </c>
+      <c r="M16">
+        <v>111.52</v>
+      </c>
+      <c r="N16">
+        <v>3510.98</v>
+      </c>
+      <c r="O16">
+        <v>3622.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1">
+        <v>45918</v>
+      </c>
+      <c r="D17">
+        <v>2925</v>
+      </c>
+      <c r="E17">
+        <v>5.4</v>
+      </c>
+      <c r="F17">
+        <v>15795</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17">
+        <v>2925</v>
+      </c>
+      <c r="I17">
+        <v>6.35</v>
+      </c>
+      <c r="J17">
+        <v>18573.75</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>2778.75</v>
+      </c>
+      <c r="M17">
+        <v>80.69</v>
+      </c>
+      <c r="N17">
+        <v>2698.06</v>
+      </c>
+      <c r="O17">
+        <v>2778.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="1">
+        <v>45919</v>
+      </c>
+      <c r="D18">
+        <v>250</v>
+      </c>
+      <c r="E18">
+        <v>38.65</v>
+      </c>
+      <c r="F18">
+        <v>9662.5</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18">
+        <v>250</v>
+      </c>
+      <c r="I18">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="J18">
+        <v>9175</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>-487.5</v>
+      </c>
+      <c r="M18">
+        <v>64.59</v>
+      </c>
+      <c r="N18">
+        <v>-552.09</v>
+      </c>
+      <c r="O18">
+        <v>487.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>156</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="1">
+        <v>45919</v>
+      </c>
+      <c r="D19">
+        <v>100</v>
+      </c>
+      <c r="E19">
+        <v>184</v>
+      </c>
+      <c r="F19">
+        <v>18400</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19">
+        <v>100</v>
+      </c>
+      <c r="I19">
+        <v>179.35</v>
+      </c>
+      <c r="J19">
+        <v>17935</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>-465</v>
+      </c>
+      <c r="M19">
+        <v>80.97</v>
+      </c>
+      <c r="N19">
+        <v>-545.97</v>
+      </c>
+      <c r="O19">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>165</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="1">
+        <v>45919</v>
+      </c>
+      <c r="D20">
+        <v>1700</v>
+      </c>
+      <c r="E20">
+        <v>19.7</v>
+      </c>
+      <c r="F20">
+        <v>33490</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20">
+        <v>1700</v>
+      </c>
+      <c r="I20">
+        <v>20.8</v>
+      </c>
+      <c r="J20">
+        <v>35360</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>1870</v>
+      </c>
+      <c r="M20">
+        <v>112.04</v>
+      </c>
+      <c r="N20">
+        <v>1757.96</v>
+      </c>
+      <c r="O20">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="1">
+        <v>45919</v>
+      </c>
+      <c r="D21">
+        <v>2925</v>
+      </c>
+      <c r="E21">
+        <v>6.75</v>
+      </c>
+      <c r="F21">
+        <v>19743.75</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21">
+        <v>2925</v>
+      </c>
+      <c r="I21">
+        <v>6.9</v>
+      </c>
+      <c r="J21">
+        <v>20182.5</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>438.75</v>
+      </c>
+      <c r="M21">
+        <v>84.76</v>
+      </c>
+      <c r="N21">
+        <v>353.99</v>
+      </c>
+      <c r="O21">
+        <v>438.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>133</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="1">
+        <v>45919</v>
+      </c>
+      <c r="D22">
+        <v>875</v>
+      </c>
+      <c r="E22">
+        <v>15.1</v>
+      </c>
+      <c r="F22">
+        <v>13212.5</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22">
+        <v>875</v>
+      </c>
+      <c r="I22">
+        <v>13.55</v>
+      </c>
+      <c r="J22">
+        <v>11856.25</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>-1356.25</v>
+      </c>
+      <c r="M22">
+        <v>70</v>
+      </c>
+      <c r="N22">
+        <v>-1426.25</v>
+      </c>
+      <c r="O22">
+        <v>1356.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>131</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="1">
+        <v>45919</v>
+      </c>
+      <c r="D23">
+        <v>3272</v>
+      </c>
+      <c r="E23">
+        <v>4.55</v>
+      </c>
+      <c r="F23">
+        <v>14887.6</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23">
+        <v>3272</v>
+      </c>
+      <c r="I23">
+        <v>5.4</v>
+      </c>
+      <c r="J23">
+        <v>17668.8</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>2781.2</v>
+      </c>
+      <c r="M23">
+        <v>79.010000000000005</v>
+      </c>
+      <c r="N23">
+        <v>2702.19</v>
+      </c>
+      <c r="O23">
+        <v>2781.2</v>
       </c>
     </row>
   </sheetData>
